--- a/inst/extdata/uncnewsletter.xlsx
+++ b/inst/extdata/uncnewsletter.xlsx
@@ -131,7 +131,7 @@
     <t xml:space="preserve">0000-0002-5778-354X</t>
   </si>
   <si>
-    <t xml:space="preserve">c("drinkingwater", "environmentalpolicy", "healthandsafety")</t>
+    <t xml:space="preserve">drinkingwater; environmentalpolicy; healthandsafety</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/ieh0rf</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">geekd@longwood.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Containerbreeding", "Mosquito", "Mosquitolarvae", "Rainwaterharvesting")</t>
+    <t xml:space="preserve">Containerbreeding; Mosquito; Mosquitolarvae; Rainwaterharvesting</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/icBZuL</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">Cape Fear River Basin (eight-digit Hydrologic Unit Code 03030002) data sets utilized for this research are as follows: NCDMS Tier 1 project sites implemented prior to December 2015 (Division of Mitigation Services, 2019) available from the North Carolina Department of Environmental Quality at https://deq.nc.gov/about/divisions/mitigation-services/dms-planning/dms-web-map; parcel data (NC OneMap Geospatial Portal, 2019) available from NC OneMap at https://www.nconemap.gov/; land-use/land-cover data (Dewitz, 2019) available from the USGS ScienceBase at https://doi.org/10.5066/P96HHBIE; total phosphorus loads (Gurley et al., 2019) available from the USGS ScienceBase at https://doi.org/10.5066/P9UUT74V; hydric soils (Soil Survey Staff, 2019) available from the USDA Natural Resources Conservation Service at https://websoilsurvey.nrcs.usda.gov/; future development probability (Sanchez et al., 2020b) available from the USGS ScienceBase at https://doi.org/10.5066/P95PTP5G.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://deq.nc.gov/about/divisions/mitigation-services/dms-planning/dms-web-map", "https://www.nconemap.gov/", "https://doi.org/10.5066/P96HHBIE", "https://doi.org/10.5066/P9UUT74V", "https://websoilsurvey.nrcs.usda.gov/", "https://doi.org/10.5066/P95PTP5G")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("compensatorymitigation", "decisionscience", "knowledgecoproduction", "naturalresourcesmanagement", "research-managementpartnerships", "watershedplanning")</t>
+    <t xml:space="preserve">https://deq.nc.gov/about/divisions/mitigation-services/dms-planning/dms-web-map; https://www.nconemap.gov/; https://doi.org/10.5066/P96HHBIE; https://doi.org/10.5066/P9UUT74V; https://websoilsurvey.nrcs.usda.gov/; https://doi.org/10.5066/P95PTP5G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compensatorymitigation; decisionscience; knowledgecoproduction; naturalresourcesmanagement; research-managementpartnerships; watershedplanning</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/itNRLc</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">lackstro@mailbox.sc.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Drought", "Communications/decision-making", "Decisionsupport", "Localeffects", "Societalimpacts", "Community")</t>
+    <t xml:space="preserve">Drought; Communications/decision-making; Decisionsupport; Localeffects; Societalimpacts; Community</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/h4G3CX</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">https://doi.org/10.15139/S3/BDQG9O</t>
   </si>
   <si>
-    <t xml:space="preserve">c("environmentaljustice", "privatewells", "toxicmetals")</t>
+    <t xml:space="preserve">environmentaljustice; privatewells; toxicmetals</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/im-ZMI</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">on request</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Escherichiacoli", "Plasmid-mediatedquinoloneresistance", "Plasmid-mediatedcolistinresistance", "Poultryworkers", "Chicken", "PoultryEnvironments", "Nigeria")</t>
+    <t xml:space="preserve">Escherichiacoli; Plasmid-mediatedquinoloneresistance; Plasmid-mediatedcolistinresistance; Poultryworkers; Chicken; PoultryEnvironments; Nigeria</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/hZ8bR1</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">0000-0002-0371-7125</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Stakeholderanalysis", "FEWS", "Environmentalsustainability", "Transdisciplinaryresearch", "Stakeholderengagement", "Livestockproduction")</t>
+    <t xml:space="preserve">Stakeholderanalysis; FEWS; Environmentalsustainability; Transdisciplinaryresearch; Stakeholderengagement; Livestockproduction</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/iadi9z</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">0000-0003-1591-3622</t>
   </si>
   <si>
-    <t xml:space="preserve">c("WaterResources", "Life", "EnvironmentalEducation", "Development", "UN2030Agenda")</t>
+    <t xml:space="preserve">WaterResources; Life; EnvironmentalEducation; Development; UN2030Agenda</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/irTmaA</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">claire.mullaney@duke.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("water", "safedrinkingwateract", "environmentallaw", "law", "policy", "publichealth", "NorthCarolina")</t>
+    <t xml:space="preserve">water; safedrinkingwateract; environmentallaw; law; policy; publichealth; NorthCarolina</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/ipmsMg</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">ekoso@smcm.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Algalblooms", "dynamicalsystems", "mathmodelling", "nutrienttresholdforresolvableblooms")</t>
+    <t xml:space="preserve">Algalblooms; dynamicalsystems; mathmodelling; nutrienttresholdforresolvableblooms</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.ajog.org/article/S0002-9378(22)01567-8/fulltext</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">Blood concentrations of per- and polyfluoroalkyl substances are associated with autoimmune-like effects in American alligators from Wilmington, North Carolina</t>
   </si>
   <si>
-    <t xml:space="preserve">c("xlsx", "docx")</t>
+    <t xml:space="preserve">xlsx; docx</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.frontiersin.org/articles/10.3389/ftox.2022.1010185/full#supplementary-material</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">The datasets presented in this study can be found in online repositories. The names of the repository/repositories and accession number(s) can be found in the article/Supplementary Material.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("autoantibodies", "autoimmune", "crocodilian", "immunetoxicity", "lupus", "onehealth")</t>
+    <t xml:space="preserve">autoantibodies; autoimmune; crocodilian; immunetoxicity; lupus; onehealth</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/h7S0S1</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">0000-0002-5347-1370</t>
   </si>
   <si>
-    <t xml:space="preserve">c("privatewells", "environmentaljustice", "drinkingwater", "testing", "metalcontamination")</t>
+    <t xml:space="preserve">privatewells; environmentaljustice; drinkingwater; testing; metalcontamination</t>
   </si>
   <si>
     <t xml:space="preserve">https://ascelibrary.org/doi/abs/10.1061/JWRMD5.WRENG-5863</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">catherine.otero@duke.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Infrastructure", "NorthCarolina", "Hurricanes", "NaturalDisasters", "PublicOpinion", "WaterSystems")</t>
+    <t xml:space="preserve">Infrastructure; NorthCarolina; Hurricanes; NaturalDisasters; PublicOpinion; WaterSystems</t>
   </si>
   <si>
     <t xml:space="preserve">https://awwa.onlinelibrary.wiley.com/doi/abs/10.1002/awwa.1977</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">ahthomp4@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Utilities", "FinancialAssistance", "Durham", "NorthCarolina")</t>
+    <t xml:space="preserve">Utilities; FinancialAssistance; Durham; NorthCarolina</t>
   </si>
   <si>
     <t xml:space="preserve">https://journals.lww.com/environepidem/Fulltext/2022/08000/Associations_between_PFAS_occurrence_and.3.aspx?context=LatestArticles</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">0000-0002-6322-4349</t>
   </si>
   <si>
-    <t xml:space="preserve">c("PFAS", "Multimorbidity", "ElectronicHealthRecords", "PFOA", "PFHpA", "Chronicdisease")</t>
+    <t xml:space="preserve">PFAS; Multimorbidity; ElectronicHealthRecords; PFOA; PFHpA; Chronicdisease</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/h2UiZf</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">0000-0001-7584-8856</t>
   </si>
   <si>
-    <t xml:space="preserve">c("DrinkingWater", "Nitrate", "Disinfectionbyproducts", "Trihalomethanes", "Exposureassessment", "Agriculture", "Cohort")</t>
+    <t xml:space="preserve">DrinkingWater; Nitrate; Disinfectionbyproducts; Trihalomethanes; Exposureassessment; Agriculture; Cohort</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/h9U0Mr</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">Effectiveness of interventions to improve drinking water, sanitation, and handwashing with soap on risk of diarrhoeal disease in children in low-income and middle-income settings: a systematic review and meta-analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">c("pdf", "xlsx")</t>
+    <t xml:space="preserve">pdf; xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">https://ars.els-cdn.com/content/image/1-s2.0-S0140673622009370-mmc1.xlsx</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">Using detrending to assess SARS-CoV-2 wastewater loads as a leading indicator of fluctuations in COVID-19 cases at fine temporal scales: Correlations across twenty sewersheds in North Carolina</t>
   </si>
   <si>
-    <t xml:space="preserve">c("pdf", "code")</t>
+    <t xml:space="preserve">pdf; code</t>
   </si>
   <si>
     <t xml:space="preserve">Kelly Hoffman</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">0000-0003-3925-1475</t>
   </si>
   <si>
-    <t xml:space="preserve">c("COVID19", "Viralload", "SARSCoV2", "Epidemiology", "Publicandoccupationalhealth", "NorthCarolina", "Diseasesurveillance", "Virustesting")</t>
+    <t xml:space="preserve">COVID19; Viralload; SARSCoV2; Epidemiology; Publicandoccupationalhealth; NorthCarolina; Diseasesurveillance; Virustesting</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/hXG2ID</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">The data is available upon request. Please contact the corresponding author.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("TropicalCyclones", "Spectralwavemodelling", "Coastalhydrodynamics", "Oceancurrents", "Stormsurge", "Barrierislands")</t>
+    <t xml:space="preserve">TropicalCyclones; Spectralwavemodelling; Coastalhydrodynamics; Oceancurrents; Stormsurge; Barrierislands</t>
   </si>
   <si>
     <t xml:space="preserve">https://link.springer.com/article/10.1007/s13157-022-01605-y</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">The datasets generated during and analyzed during the current study are available from the corresponding author on reasonable request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Pocosin", "Greenhousegases", "Restoration", "Mitigation")</t>
+    <t xml:space="preserve">Pocosin; Greenhousegases; Restoration; Mitigation</t>
   </si>
   <si>
     <t xml:space="preserve">https://link.springer.com/article/10.1007/s10980-022-01425-9</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">All data used in this study was publicly available online. Eddy covariance data was downloaded from Ameriflux (https://ameriflux.lbl.gov/sites/siteinfo/US-Cwt). GRIDMET SPI data, land cover data, and USGS NED data was downloaded from Google Earth Engine (https://earthengine.google.com/). MODIS ET data was downloaded from USGS (https://lpdaac.usgs.gov/products/mod16a2gfv006/). Landsat ET data was downloaded from USGS (https://www.usgs.gov/core-science-systems/nli/landsat/landsat-provisional-actual-evapotranspiration). The Riley et al. (2021) forest composition map was downloaded from the USDA Forest Service (https://www.fs.usda.gov/rds/archive/Catalog/RDS-2019-0026). The Wilson et al. (2013) forest composition maps were downloaded from the USDA forest service (https://www.fs.usda.gov/rds/archive/catalog/RDS-2013-0013).</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://ameriflux.lbl.gov/sites/siteinfo/US-Cwt", "https://earthengine.google.com", "https://lpdaac.usgs.gov/products/mod16a2gfv006", "https://www.usgs.gov/core-science-systems/nli/landsat/landsat-provisional-actual-evapotranspiration", "https://www.fs.usda.gov/rds/archive/Catalog/RDS-2019-0026", "https://www.fs.usda.gov/rds/archive/catalog/RDS-2013-0013")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("Evapotranspiration", "Remotesensing", "Topography", "Forestcomposition", "Landsat", "MODIS")</t>
+    <t xml:space="preserve">https://ameriflux.lbl.gov/sites/siteinfo/US-Cwt; https://earthengine.google.com; https://lpdaac.usgs.gov/products/mod16a2gfv006; https://www.usgs.gov/core-science-systems/nli/landsat/landsat-provisional-actual-evapotranspiration; https://www.fs.usda.gov/rds/archive/Catalog/RDS-2019-0026; https://www.fs.usda.gov/rds/archive/catalog/RDS-2013-0013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evapotranspiration; Remotesensing; Topography; Forestcomposition; Landsat; MODIS</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.pnas.org/doi/10.1073/pnas.2216021120</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">Data (calculator and programming code) have been deposited in Covid-SURGE toolkit (21). Anonymized wastewater and case count data have been deposited in NC COVID dashboard (20). Some study data are available. The use of the Covid-SURGE algorithm or calculator beyond the scope of the CC BY-NC-ND 2.0 license is subject to permission being granted by Mathematica.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://wastewater.covidsurge.mathematica.org", "https://covid19.ncdhhs.gov/dashboard/data-behind-dashboards")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("WastewaterMonitoring", "Sars-Covid-2", "Covid-19Surge", "EarlyWarning", "AlertAlgorithm")</t>
+    <t xml:space="preserve">https://wastewater.covidsurge.mathematica.org; https://covid19.ncdhhs.gov/dashboard/data-behind-dashboards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WastewaterMonitoring; Sars-Covid-2; Covid-19Surge; EarlyWarning; AlertAlgorithm</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.pnas.org/doi/abs/10.1073/pnas.2120252120</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">https://doi.org/10.7910/DVN/XT3RZ8</t>
   </si>
   <si>
-    <t xml:space="preserve">c("NonmarketEvaluation", "Waterquality", "Urbanstreams", "Statedpreference")</t>
+    <t xml:space="preserve">NonmarketEvaluation; Waterquality; Urbanstreams; Statedpreference</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.pnas.org/content/119/6/e2110694119.short</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">Anonymized de-identified children's blood Pb, water source, household information, census block group information, and juvenile justice report data have been deposited in https://scholarworks.iu.edu/dspace/handle/2022/27027 (72, 73). https://scholarworks.iu.edu/dspace/handle/2022/25638.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://scholarworks.iu.edu/dspace/handle/2022/27027", "https://scholarworks.iu.edu/dspace/handle/2022/25638")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("Drinkingwater", "Children", "Leadexposure")</t>
+    <t xml:space="preserve">https://scholarworks.iu.edu/dspace/handle/2022/27027; https://scholarworks.iu.edu/dspace/handle/2022/25638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drinkingwater; Children; Leadexposure</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.tandfonline.com/doi/abs/10.1080/21622515.2023.2182719</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">0000-0002-3317-7318</t>
   </si>
   <si>
-    <t xml:space="preserve">c("FaecalSludgeTreatment", "Composting", "Temperature-timecritera", "pathogeninactivationmechanism", "compostsanitation")</t>
+    <t xml:space="preserve">FaecalSludgeTreatment; Composting; Temperature-timecritera; pathogeninactivationmechanism; compostsanitation</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.tandfonline.com/doi/full/10.1080/09640568.2023.2183112</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">0000-0003-2315-7062</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Hazardmitigation", "compoundevent", "flooding", "ruralresilience", "climatechange")</t>
+    <t xml:space="preserve">Hazardmitigation; compoundevent; flooding; ruralresilience; climatechange</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.tandfonline.com/doi/abs/10.1080/02626667.2022.2052073</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">0000-0003-3160-5363</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Environmentaljustive", "Ambientwaterquality", "Interfaceswithsociety")</t>
+    <t xml:space="preserve">Environmentaljustive; Ambientwaterquality; Interfaceswithsociety</t>
   </si>
   <si>
     <t xml:space="preserve">https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2021WR031533</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">https://www.hydroshare.org/resource/b9fb89d2539c4e43b51889770f7a81f7</t>
   </si>
   <si>
-    <t xml:space="preserve">c("urban", "nonpointsource", "watershed", "nitrogen", "hydrology", "management")</t>
+    <t xml:space="preserve">urban; nonpointsource; watershed; nitrogen; hydrology; management</t>
   </si>
   <si>
     <t xml:space="preserve">https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2021WR030711</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">https://doi.org/10.4211/hs.c169de42e6174baf842a319efe28a75e</t>
   </si>
   <si>
-    <t xml:space="preserve">c("sandhills", "seepageflux", "groundwater", "surfacewater", "spatialvariability", "hydrology")</t>
+    <t xml:space="preserve">sandhills; seepageflux; groundwater; surfacewater; spatialvariability; hydrology</t>
   </si>
   <si>
     <t xml:space="preserve">https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2021WR030700</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">All WaterPaths modeling code used to simulate Triangle water supply decision-making can be found at https://github.com/bernardoct/WaterPaths/tree/JLWTPAgreementsModel. All additional modeling code, input and output data for producing the results of this manuscript can be accessed at https://www.hydroshare.org/resource/3fc8e01960d948a2bd38189dd4e7fa69/.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://github.com/bernardoct/WaterPaths/tree/JLWTPAgreementsModel", "https://www.hydroshare.org/resource/3fc8e01960d948a2bd38189dd4e7fa69")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("waterutility", "cooperation", "demand", "deepuncertainty", "optimization", "financialrisk")</t>
+    <t xml:space="preserve">https://github.com/bernardoct/WaterPaths/tree/JLWTPAgreementsModel; https://www.hydroshare.org/resource/3fc8e01960d948a2bd38189dd4e7fa69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">waterutility; cooperation; demand; deepuncertainty; optimization; financialrisk</t>
   </si>
   <si>
     <t xml:space="preserve">https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2021EF002139</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">Data and code used in the analyses are freely available on GitHub (https://github.com/acgold/HTF-on-roads) and Zenodo.org (https://doi.org/10.5281/zenodo.5562568).</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://github.com/acgold/HTF-on-roads", "https://doi.org/10.5281/zenodo.5562568")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("coastaldevelopment", "stormwatermanagement", "infrastructure", "inundationmodeling", "high-tideflooding")</t>
+    <t xml:space="preserve">https://github.com/acgold/HTF-on-roads; https://doi.org/10.5281/zenodo.5562568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coastaldevelopment; stormwatermanagement; infrastructure; inundationmodeling; high-tideflooding</t>
   </si>
   <si>
     <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/full/10.1002/esp.5495</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">in paper or supp</t>
   </si>
   <si>
-    <t xml:space="preserve">c("erosion", "land-usechange", "legacysediment", "slope-areatreshold", ".", "soilnutrients", "streamchannelinitiation")</t>
+    <t xml:space="preserve">erosion; land-usechange; legacysediment; slope-areatreshold; .; soilnutrients; streamchannelinitiation</t>
   </si>
   <si>
     <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/abs/10.1111/psj.12473</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">External drivers of participation in regional collaborative water planning</t>
   </si>
   <si>
-    <t xml:space="preserve">c("collaborativegovernance", "policybeliefs", "regionalwaterplanning", "Gobernanzacolaborativa", "creenciaspolíticas", "planificaciónregionaldelagua", "协作治理", "政策信念", "区域水资源规划")</t>
+    <t xml:space="preserve">collaborativegovernance; policybeliefs; regionalwaterplanning; Gobernanzacolaborativa; creenciaspolíticas; planificaciónregionaldelagua; 协作治理; 政策信念; 区域水资源规划</t>
   </si>
   <si>
     <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/epdf/10.1002/anie.202208150</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">https://www.hydroshare.org/resource/957475e1101346a6a1cbbb62f17e747d</t>
   </si>
   <si>
-    <t xml:space="preserve">c("biology-geologyfeebacks", "DMQ99", "evapotranspiration", "headwaterstreams", "landusechange", "seasonalflashiness", "specificconductance", "streamgauges")</t>
+    <t xml:space="preserve">biology-geologyfeebacks; DMQ99; evapotranspiration; headwaterstreams; landusechange; seasonalflashiness; specificconductance; streamgauges</t>
   </si>
   <si>
     <t xml:space="preserve">https://scholar.google.com/scholar_url?url=https://ajph.aphapublications.org/doi/pdf/10.2105/AJPH.2022.307003%3Fdownload%3Dtrue&amp;hl=en&amp;sa=X&amp;d=3962241131938486649&amp;ei=H1Q7Y6aFPO2KywSS3bH4Bg&amp;scisig=AAGBfm3Q4X2sCbJJGTgTcSrsGU_FdUVJcw&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:7463423130094204642:AAGBfm306n8jEm7p9E06Y9mqflGSBiV6Pg&amp;html=&amp;pos=0&amp;folt=kw-top</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">0000-0001-6231-9437</t>
   </si>
   <si>
-    <t xml:space="preserve">c("WASP", "environmentalmodeling", "nanocopper", "nanomaterials", "freswater")</t>
+    <t xml:space="preserve">WASP; environmentalmodeling; nanocopper; nanomaterials; freswater</t>
   </si>
   <si>
     <t xml:space="preserve">https://scholar.google.com/scholar_url?url=https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/hir.12445&amp;hl=en&amp;sa=X&amp;d=7293212103073901469&amp;ei=2fm2YrzQKtHjmQGNwb84&amp;scisig=AAGBfm1zjx3-V2aCgS0L1xZx26MYDvF-tg&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:3552202248086981277:AAGBfm3xoOKMdpREzJ__fgBb7pdlMpLHFA&amp;html=&amp;pos=1&amp;folt=kw</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">0000-0001-7360-0021</t>
   </si>
   <si>
-    <t xml:space="preserve">c("healtheducation", "healthinformationneeds", "healthprofessionals", "informationdissemination", "informationliteracy", "informationseekingbehavior", "patienteducation", "research", "qualitative")</t>
+    <t xml:space="preserve">healtheducation; healthinformationneeds; healthprofessionals; informationdissemination; informationliteracy; informationseekingbehavior; patienteducation; research; qualitative</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/ivRR62</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">0000-0002-6373-8374</t>
   </si>
   <si>
-    <t xml:space="preserve">c("crAssphage", "Municipaluntreatedwastewater", "Temporalvariations", "Spatialvariations", "Entericpathogenscorrelations", "Bacteria", "Andviruses", ";", "qPCR", "rt-qPCR")</t>
+    <t xml:space="preserve">crAssphage; Municipaluntreatedwastewater; Temporalvariations; Spatialvariations; Entericpathogenscorrelations; Bacteria; Andviruses; ;; qPCR; rt-qPCR</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/36633899/</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">The codes used in this research are available from the authors upon request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("ArtificialNeuralNetworks", "Geneticprogramming", "Antedcedentenvironmentalconditions", "Temperature", "Salinity", "Oysters")</t>
+    <t xml:space="preserve">ArtificialNeuralNetworks; Geneticprogramming; Antedcedentenvironmentalconditions; Temperature; Salinity; Oysters</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/36356280/</t>
@@ -1742,11 +1742,10 @@
     <t xml:space="preserve">The raw sequencing data (FASTQ) generated in this study have been deposited in the European Nucleotide Archive and can be accessed without restrictions. The data from major sampling rounds have the following project accession numbers: PRJEB40798, PRJEB40816, PRJEB40815 and PRJEB27621. Sequencing data from the longitudinal city sampling sites are deposited under PRJEB51229, while the included datasets from the previous study are deposited under ERP015409. See Supplementary Data 1 for exact sample, experiment and run accessions. Source data are provided with this paper. This study also utilized the publicly available databases of ResFinder, PLSDB, Silva and Kraken 2.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://www.ebi.ac.uk/ena/browser/view/PRJEB40798", "https://www.ebi.ac.uk/ena/browser/view/PRJEB40816", "https://www.ebi.ac.uk/ena/browser/view/PRJEB40815", "https://www.ebi.ac.uk/ena/browser/view/PRJEB27621", "https://www.ebi.ac.uk/ena/browser/view/PRJEB51229", "https://www.ebi.ac.uk/ena/browser/view/ERP015409", "https://bitbucket.org/genomicepidemiology/resfinder_db", "https://ccb-microbe.cs.uni-saarland.de/plsdb/plasmids/download/", "https://www.arb-silva.de/download/arb-files/", "https://benlangmead.github.io/aws-indexes/k2"
-)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("Antimicrobialresistance", "Metagenomics", "Microbialecology", "Policyandpublichealthinmicrobiology")</t>
+    <t xml:space="preserve">https://www.ebi.ac.uk/ena/browser/view/PRJEB40798; https://www.ebi.ac.uk/ena/browser/view/PRJEB40816; https://www.ebi.ac.uk/ena/browser/view/PRJEB40815; https://www.ebi.ac.uk/ena/browser/view/PRJEB27621; https://www.ebi.ac.uk/ena/browser/view/PRJEB51229; https://www.ebi.ac.uk/ena/browser/view/ERP015409; https://bitbucket.org/genomicepidemiology/resfinder_db; https://ccb-microbe.cs.uni-saarland.de/plsdb/plasmids/download/; https://www.arb-silva.de/download/arb-files/; https://benlangmead.github.io/aws-indexes/k2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antimicrobialresistance; Metagenomics; Microbialecology; Policyandpublichealthinmicrobiology</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.nature.com/articles/s41370-022-00475-0</t>
@@ -1773,7 +1772,7 @@
     <t xml:space="preserve">The datasets generated during and/or analyzed during the current study are available from the corresponding author on reasonable request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Pretermbirth", "Lowbirthweight", "Adversebirthoutcome", "Pollutedsites", "Superfund", "Industrialsites")</t>
+    <t xml:space="preserve">Pretermbirth; Lowbirthweight; Adversebirthoutcome; Pollutedsites; Superfund; Industrialsites</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.nature.com/articles/s43247-022-00501-x</t>
@@ -1812,7 +1811,7 @@
     <t xml:space="preserve">https://doi.org/10.6084/m9.figshare.20137649.v265</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Carboncycle", "Climate-changemitigation", "Environmentalimpact")</t>
+    <t xml:space="preserve">Carboncycle; Climate-changemitigation; Environmentalimpact</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.nature.com/articles/s41545-021-00128-z</t>
@@ -1845,7 +1844,7 @@
     <t xml:space="preserve">no data generated</t>
   </si>
   <si>
-    <t xml:space="preserve">c("ChemicalEngineering", "Waterresources")</t>
+    <t xml:space="preserve">ChemicalEngineering; Waterresources</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.nature.com/articles/s41597-022-01358-7</t>
@@ -1876,10 +1875,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://github.com/TransformingDrainageProject/Drain-Flow-Gap-Filling", "https://github.com/isudatateam/datateam")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("Agriculture", "Environmentalimpact", "Hydrology", "Waterresources")</t>
+    <t xml:space="preserve">https://github.com/TransformingDrainageProject/Drain-Flow-Gap-Filling; https://github.com/isudatateam/datateam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture; Environmentalimpact; Hydrology; Waterresources</t>
   </si>
   <si>
     <t xml:space="preserve">https://journals.plos.org/plosntds/article?id=10.1371/journal.pntd.0011496</t>
@@ -1948,7 +1947,7 @@
     <t xml:space="preserve">Field performance of the GaugeCam image-based water level measurement system</t>
   </si>
   <si>
-    <t xml:space="preserve">c("docx", "tif")</t>
+    <t xml:space="preserve">docx; tif</t>
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.1371/journal.pwat.0000032.s001</t>
@@ -2077,7 +2076,7 @@
     <t xml:space="preserve">mark_sobsey@unc.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Cryptosporidium", "Bacillusspores", "MS2coliphage", "bromine", "chlorine", "disinfection", "watertreatment")</t>
+    <t xml:space="preserve">Cryptosporidium; Bacillusspores; MS2coliphage; bromine; chlorine; disinfection; watertreatment</t>
   </si>
   <si>
     <t xml:space="preserve">32</t>
@@ -2110,7 +2109,7 @@
     <t xml:space="preserve">0000-0003-1315-1791</t>
   </si>
   <si>
-    <t xml:space="preserve">c("PFASdestruction", "fluoroethers", "GenX", "Nafionbyproduct2", "photolysis")</t>
+    <t xml:space="preserve">PFASdestruction; fluoroethers; GenX; Nafionbyproduct2; photolysis</t>
   </si>
   <si>
     <t xml:space="preserve">35</t>
@@ -2149,10 +2148,10 @@
     <t xml:space="preserve">The storm drain water level data used for flood detection and analysis in the study are archived on Zenodo (https://doi.org/10.5281/zenodo.7135955) and can also be downloaded from our project web app (https://sunnydayflood.apps.cloudapps.unc.edu). The software for the SuDS sensor framework are available on GitHub (https://github.com/sunny-day-flooding-project) and tutorials are archived on Zenodo (Hayden-Lowe et al., 2022, https://doi.org/10.5281/zenodo.7017187).</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://doi.org/10.5281/zenodo.7135955", "https://sunnydayflood.apps.cloudapps.unc.edu", "https://github.com/sunny-day-flooding-project", "https://doi.org/10.5281/zenodo.7017187")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("coastalflooding", "low-costsensors", "hightideflooding", "stormwatermanagement", "coastalinfrastructure", "sealevelrise")</t>
+    <t xml:space="preserve">https://doi.org/10.5281/zenodo.7135955; https://sunnydayflood.apps.cloudapps.unc.edu; https://github.com/sunny-day-flooding-project; https://doi.org/10.5281/zenodo.7017187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coastalflooding; low-costsensors; hightideflooding; stormwatermanagement; coastalinfrastructure; sealevelrise</t>
   </si>
   <si>
     <t xml:space="preserve">39</t>
@@ -2164,7 +2163,7 @@
     <t xml:space="preserve">Affordability of household water services across the United States</t>
   </si>
   <si>
-    <t xml:space="preserve">c("docx", "csv")</t>
+    <t xml:space="preserve">docx; csv</t>
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.1371/journal.pwat.0000123.s001</t>
@@ -2209,7 +2208,7 @@
     <t xml:space="preserve">Anonymized data can be shared upon request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("PFAS", "Drinkingwater", "USEPA", "PFPrA", "Ultra-shortchain")</t>
+    <t xml:space="preserve">PFAS; Drinkingwater; USEPA; PFPrA; Ultra-shortchain</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2306-5338/10/7/156</t>
@@ -2242,7 +2241,7 @@
     <t xml:space="preserve">Raw data can be provided upon request by emailing the corresponding author at Humphreyc@ecu.edu.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("coastal", "fecalbacteria", "runoff", "stormwater")</t>
+    <t xml:space="preserve">coastal; fecalbacteria; runoff; stormwater</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2073-4441/15/13/2436</t>
@@ -2269,7 +2268,7 @@
     <t xml:space="preserve">The data presented in this study are available on request from the corresponding author.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("cyanobacteria", "cyanotoxin", "microcystin", "stormwaterpollution", "eutrophication")</t>
+    <t xml:space="preserve">cyanobacteria; cyanotoxin; microcystin; stormwaterpollution; eutrophication</t>
   </si>
   <si>
     <t xml:space="preserve">http://eepurl.com/ikRgmb</t>
@@ -2296,7 +2295,7 @@
     <t xml:space="preserve">0000-0002-0944-8632</t>
   </si>
   <si>
-    <t xml:space="preserve">c("waterscarcity", "waterrecycling", "wastewatertreatmentplants", "nutrients", "phosphorus")</t>
+    <t xml:space="preserve">waterscarcity; waterrecycling; wastewatertreatmentplants; nutrients; phosphorus</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/1422-0067/24/2/1295</t>
@@ -2335,7 +2334,7 @@
     <t xml:space="preserve">Data included in this study are available from the corresponding author upon reasonable request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("HWTS", "POU", "chitosan", "coagulation", "sandfiltration", "bacterialreduction", "virusreduction")</t>
+    <t xml:space="preserve">HWTS; POU; chitosan; coagulation; sandfiltration; bacterialreduction; virusreduction</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2073-4441/14/13/2088</t>
@@ -2362,7 +2361,7 @@
     <t xml:space="preserve">jozo@sfsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("explainability", "LSPmethod", "waterquality", "decision-making")</t>
+    <t xml:space="preserve">explainability; LSPmethod; waterquality; decision-making</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2306-5338/9/12/218</t>
@@ -2389,10 +2388,10 @@
     <t xml:space="preserve">All publicly available datasets used in this research are available at the locations indicated in Table 1 or upon request in their processed version from the corresponding author.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://coast.noaa.gov/slrdata/", "https://coast.noaa.gov/slrdata/", "https://fris.nc.gov/fris/Home.aspx?ST=NC", "https://earthexplorer.usgs.gov/", "https://deq.nc.gov/about/divisions/coastal", "https://www.nconemap.gov/pages/parcels")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("wetlands", "nature-basedsolutions", "floodmitigation", "coastalflooding", "tidalwatersheds")</t>
+    <t xml:space="preserve">https://coast.noaa.gov/slrdata/; https://coast.noaa.gov/slrdata/; https://fris.nc.gov/fris/Home.aspx?ST=NC; https://earthexplorer.usgs.gov/; https://deq.nc.gov/about/divisions/coastal; https://www.nconemap.gov/pages/parcels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wetlands; nature-basedsolutions; floodmitigation; coastalflooding; tidalwatersheds</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2076-3417/12/19/10159/pdf?version=1665394404</t>
@@ -2407,7 +2406,7 @@
     <t xml:space="preserve">https://www.mdpi.com/article/10.3390/app121910159/s1</t>
   </si>
   <si>
-    <t xml:space="preserve">c("reclaimedwater", "waterreuse", "water-supplysystems", "agro-wastewater", "riskassessment")</t>
+    <t xml:space="preserve">reclaimedwater; waterreuse; water-supplysystems; agro-wastewater; riskassessment</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2073-445X/11/9/1504/htm</t>
@@ -2437,10 +2436,10 @@
     <t xml:space="preserve">The data presented in this study are available in Appendix A.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://www.nconemap.gov/", "https://www.nrcs.usda.gov/wps/portal/nrcs/detail/soils/survey/geo/?cid=nrcs142p2_053628", "https://www.nconemap.gov/", "https://www.nconemap.gov/")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("geospatialanalysis", "landsuitability", "floodmitigation", "nature-basedsolutions(NBS)", "rurallandscapes", "GeographicInformationSystems(GIS)", "floodresilience")</t>
+    <t xml:space="preserve">https://www.nconemap.gov/; https://www.nrcs.usda.gov/wps/portal/nrcs/detail/soils/survey/geo/?cid=nrcs142p2_053628; https://www.nconemap.gov/; https://www.nconemap.gov/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geospatialanalysis; landsuitability; floodmitigation; nature-basedsolutions(NBS); rurallandscapes; GeographicInformationSystems(GIS); floodresilience</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2076-3417/12/19/10159</t>
@@ -2461,7 +2460,7 @@
     <t xml:space="preserve">Data are summarized and displayed in figures. Raw data may be made available via email with the corresponding author.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("coastal", "eutrophicationsepticsystems")</t>
+    <t xml:space="preserve">coastal; eutrophicationsepticsystems</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2073-4441/14/10/1525/pdf?version=1652171768</t>
@@ -2479,7 +2478,7 @@
     <t xml:space="preserve">jdyer@geosci.msstate.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("hydrologicdrought", "SoutheastUS", "NationalWaterModel")</t>
+    <t xml:space="preserve">hydrologicdrought; SoutheastUS; NationalWaterModel</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/1660-4601/19/8/4628/pdf</t>
@@ -2509,10 +2508,10 @@
     <t xml:space="preserve">The data for socioeconomic vulnerability variables can be found through API of American Community Survey [62]. Data for community access to safe drinking water are openly available at Safe Drinking Water Information System (SDWIS) [63]. Land cover raster maps of 2019 and 2016 can be found at Multi-Resolution Land Characteristic Consortium (MRLC) website [64]. To access drought data, we used the Comprehensive Statistics page of Data Download section of U.S. Drought Monitor [65]. The data that support the findings of this study are openly available in Mendeley Data [66].</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://www.census.gov/data/developers/data-sets/acs-5year.html", "https://www.epa.gov/ground-water-and-drinking-water/safe-drinking-water-information-system-sdwis-federal-reporting")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("droughtandhealth", "droughtrisk", "LocalMoran", "sI", "droughtvulnerability", "U.S.drought")</t>
+    <t xml:space="preserve">https://www.census.gov/data/developers/data-sets/acs-5year.html; https://www.epa.gov/ground-water-and-drinking-water/safe-drinking-water-information-system-sdwis-federal-reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">droughtandhealth; droughtrisk; LocalMoran; sI; droughtvulnerability; U.S.drought</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2071-1050/14/7/3889/pdf</t>
@@ -2539,7 +2538,7 @@
     <t xml:space="preserve">0000-0002-2834-3764</t>
   </si>
   <si>
-    <t xml:space="preserve">c("environmentalplanning", "policyevaluation", "riparianbuffers")</t>
+    <t xml:space="preserve">environmentalplanning; policyevaluation; riparianbuffers</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/1999-4907/13/3/411</t>
@@ -2572,7 +2571,7 @@
     <t xml:space="preserve">https://github.com/hkqcqq/CoastalWetlandDetection.git</t>
   </si>
   <si>
-    <t xml:space="preserve">c("coastalwetlanddegradation", "remotesensing", "NDVI", "climatechange", "sea-levelrise", "saltwaterintrusion", "hydrologicmodel", "AlligatorRiverNationalWildlifeRefuge", "USA")</t>
+    <t xml:space="preserve">coastalwetlanddegradation; remotesensing; NDVI; climatechange; sea-levelrise; saltwaterintrusion; hydrologicmodel; AlligatorRiverNationalWildlifeRefuge; USA</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.mdpi.com/2073-4441/14/2/247</t>
@@ -2602,7 +2601,7 @@
     <t xml:space="preserve">https://doi.org/10.7910/DVN/0ETQ74</t>
   </si>
   <si>
-    <t xml:space="preserve">c("waterinfrastructure", "waterservices", "waterutilities", "waterbills", "billingfrequency", "customerassistanceprograms(CAPS)", "affordability")</t>
+    <t xml:space="preserve">waterinfrastructure; waterservices; waterutilities; waterbills; billingfrequency; customerassistanceprograms(CAPS); affordability</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.est.3c01146</t>
@@ -2629,7 +2628,7 @@
     <t xml:space="preserve">0000-0003-2954-1110</t>
   </si>
   <si>
-    <t xml:space="preserve">c("canine", "drinkingwater", "equine", "fluoroether", "OneHealth", "nafionby-product2", "GenXchemicals", "PFOA", "PFOS")</t>
+    <t xml:space="preserve">canine; drinkingwater; equine; fluoroether; OneHealth; nafionby-product2; GenXchemicals; PFOA; PFOS</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.estlett.0c00255</t>
@@ -2653,7 +2652,7 @@
     <t xml:space="preserve">0000-0002-5289-1218</t>
   </si>
   <si>
-    <t xml:space="preserve">c("drinkingwater", "fluoropolymers", "food", "safety", "toxins")</t>
+    <t xml:space="preserve">drinkingwater; fluoropolymers; food; safety; toxins</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.estlett.3c00487</t>
@@ -2665,7 +2664,7 @@
     <t xml:space="preserve">jmacdon@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Airpollution", "Color", "Environmentalpollution", "Environmentalscience", "Impurities")</t>
+    <t xml:space="preserve">Airpollution; Color; Environmentalpollution; Environmentalscience; Impurities</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.est.2c07477</t>
@@ -2674,7 +2673,7 @@
     <t xml:space="preserve">Improved Decision Making for Water Lead Testing in U.S. Child Care Facilities Using Machine-Learned Bayesian Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">c("pdf", "html")</t>
+    <t xml:space="preserve">pdf; html</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.est.2c07477?goto=supporting-info</t>
@@ -2698,7 +2697,7 @@
     <t xml:space="preserve">https://doi.org/10.5281/zenodo.7477787</t>
   </si>
   <si>
-    <t xml:space="preserve">c("lead", "Children", "shealth", "drinkingwater", "machinelearning", "riskassessment")</t>
+    <t xml:space="preserve">lead; Children; shealth; drinkingwater; machinelearning; riskassessment</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/full/10.1021/acs.est.2c07316</t>
@@ -2728,7 +2727,7 @@
     <t xml:space="preserve">0000-0001-6220-8673</t>
   </si>
   <si>
-    <t xml:space="preserve">c("PFASair-waterinterfacialadsorption", "QSPR", "nonequilibrium", "unsaturatedcolumns", "panfilm")</t>
+    <t xml:space="preserve">PFASair-waterinterfacialadsorption; QSPR; nonequilibrium; unsaturatedcolumns; panfilm</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.accounts.2c00591</t>
@@ -2749,7 +2748,7 @@
     <t xml:space="preserve">soobare@ncat.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("adsorption", "molecules", "nanofibers", "remediation")</t>
+    <t xml:space="preserve">adsorption; molecules; nanofibers; remediation</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acsestwater.2c00320</t>
@@ -2779,7 +2778,7 @@
     <t xml:space="preserve">0000-0001-5246-2213</t>
   </si>
   <si>
-    <t xml:space="preserve">c("nontargetedanalysis", "anthropogenicchemicals", "wastewater", "landfillleachate", "reverseosmosis")</t>
+    <t xml:space="preserve">nontargetedanalysis; anthropogenicchemicals; wastewater; landfillleachate; reverseosmosis</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/full/10.1021/acs.estlett.2c00502?cookieSet=1</t>
@@ -2812,7 +2811,7 @@
     <t xml:space="preserve">0000-0001-5223-2848</t>
   </si>
   <si>
-    <t xml:space="preserve">c("per-andpolyfluoroalkylsubstances(PFAS)", "presumptivecontamination", "PFAStestingandinvestigation", "AFFF", "PFASwasteanddisposal")</t>
+    <t xml:space="preserve">per-andpolyfluoroalkylsubstances(PFAS); presumptivecontamination; PFAStestingandinvestigation; AFFF; PFASwasteanddisposal</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/full/10.1021/acsestwater.2c00287?cookieSet=1</t>
@@ -2833,7 +2832,7 @@
     <t xml:space="preserve">0000-0001-9488-8124</t>
   </si>
   <si>
-    <t xml:space="preserve">c("anatomy", "genetics", "infectiousdiseases", "viruses", "wastewater")</t>
+    <t xml:space="preserve">anatomy; genetics; infectiousdiseases; viruses; wastewater</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.est.2c04717?cookieSet=1</t>
@@ -2863,7 +2862,7 @@
     <t xml:space="preserve">0000-0001-8928-0157</t>
   </si>
   <si>
-    <t xml:space="preserve">c("coalash", "lacustrinesediment", "multiproxytracing", "aquaticecosystems")</t>
+    <t xml:space="preserve">coalash; lacustrinesediment; multiproxytracing; aquaticecosystems</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.est.2c03076</t>
@@ -2884,7 +2883,7 @@
     <t xml:space="preserve">0000-0003-1966-2680</t>
   </si>
   <si>
-    <t xml:space="preserve">c("waterandsanitationinfrastructure", "disadvantagedunincorporatedcommunities", "environmetaljustice", "participatoryprocess", "sociotechnicaldesign")</t>
+    <t xml:space="preserve">waterandsanitationinfrastructure; disadvantagedunincorporatedcommunities; environmetaljustice; participatoryprocess; sociotechnicaldesign</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/abs/10.1021/acsapm.2c00959</t>
@@ -2914,7 +2913,7 @@
     <t xml:space="preserve">0000-0003-3395-4823</t>
   </si>
   <si>
-    <t xml:space="preserve">c("textiledyes", "environmentalpollution", "cleanwater", "sustainability", "polycarbodiimide", "topologicalpolarsurfacearea(TPSA)", "moleculartransport")</t>
+    <t xml:space="preserve">textiledyes; environmentalpollution; cleanwater; sustainability; polycarbodiimide; topologicalpolarsurfacearea(TPSA); moleculartransport</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.est.2c00224</t>
@@ -2941,7 +2940,7 @@
     <t xml:space="preserve">marc_serre@unc.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("land-useregression", "molecularmicrobialsourcetracking", "surfacewater", "sediment", "rivernetworks", "animalfeedingoperations", "septicsystems")</t>
+    <t xml:space="preserve">land-useregression; molecularmicrobialsourcetracking; surfacewater; sediment; rivernetworks; animalfeedingoperations; septicsystems</t>
   </si>
   <si>
     <t xml:space="preserve">https://pubs.acs.org/doi/10.1021/acs.est.1c05683</t>
@@ -2962,7 +2961,7 @@
     <t xml:space="preserve">swdaly@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("multiplewatersourceuse", "supplementalunimprovedsourceuse", "fecalcontamination", "MonteCarlosimulations", "drinkingwaterquality", "low-andmiddle-incomecountries")</t>
+    <t xml:space="preserve">multiplewatersourceuse; supplementalunimprovedsourceuse; fecalcontamination; MonteCarlosimulations; drinkingwaterquality; low-andmiddle-incomecountries</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0043135423005481</t>
@@ -2992,7 +2991,7 @@
     <t xml:space="preserve">Data will be made available on request</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Microplasticsinrivers", "Watermanagement", "DiversionsAbstraction", "Pairedcatchmentapproach", "Globalmodels")</t>
+    <t xml:space="preserve">Microplasticsinrivers; Watermanagement; DiversionsAbstraction; Pairedcatchmentapproach; Globalmodels</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0925857423001209</t>
@@ -3016,7 +3015,7 @@
     <t xml:space="preserve">curtr@duke.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Pocosin", "Carbon", "Methane", "GHG", "Netecosystemexchange", "Hydrologicrestoration", "Peatland", "Evergreenshrubbog", "Watertabledepth", "Eddycovariance", "", "Carbondioxide")</t>
+    <t xml:space="preserve">Pocosin; Carbon; Methane; GHG; Netecosystemexchange; Hydrologicrestoration; Peatland; Evergreenshrubbog; Watertabledepth; Eddycovariance; Carbondioxide</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969723037142</t>
@@ -3040,7 +3039,7 @@
     <t xml:space="preserve">sam.hall@alumni.duke.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Per-andpolyfluoroalkylsubstances", "PFAS", "Drinkingwater", "Serum", "Humanhealthoutcomes")</t>
+    <t xml:space="preserve">Per-andpolyfluoroalkylsubstances; PFAS; Drinkingwater; Serum; Humanhealthoutcomes</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0160412023003069?via%3Dihub</t>
@@ -3070,10 +3069,10 @@
     <t xml:space="preserve">All data are available. All data presented can be found in a series of USGS data releases (Meppelink et al., 2022, Romanok and Bradley, 2018, Romanok and Bradley, 2021, Romanok et al., 2022, Romanok et al., 2019, Romanok et al., 2023a, Romanok et al., 2023b, Romanok et al., 2023c). For links to the individual USGS data releases see Table S1.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://www.sciencebase.gov/catalog/item/5fad56aad34eb413d5df459c", "https://www.sciencebase.gov/catalog/item/5ab3d60be4b081f61ab5e3d4")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("Per-andpolyfluoroalkylsubstances", "Drinking-water", "Public-supply", "Private-wellsSources", "Healtheffect")</t>
+    <t xml:space="preserve">https://www.sciencebase.gov/catalog/item/5fad56aad34eb413d5df459c; https://www.sciencebase.gov/catalog/item/5ab3d60be4b081f61ab5e3d4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-andpolyfluoroalkylsubstances; Drinking-water; Public-supply; Private-wellsSources; Healtheffect</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0043135423005523?via%3Dihub</t>
@@ -3103,7 +3102,7 @@
     <t xml:space="preserve">cstauber@gsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Zikavirus", "wastewater-basedepidemiology", "resource-constrainedsettings")</t>
+    <t xml:space="preserve">Zikavirus; wastewater-basedepidemiology; resource-constrainedsettings</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S2213343723012411?via%3Dihub</t>
@@ -3136,7 +3135,7 @@
     <t xml:space="preserve">No data was used for the research described in the article.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Airpollutioncontrol", "Biologicalgastreatment", "Capillaryreactor", "Hydrophobicpollutants", "Segmentedflow")</t>
+    <t xml:space="preserve">Airpollutioncontrol; Biologicalgastreatment; Capillaryreactor; Hydrophobicpollutants; Segmentedflow</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969723027080?via%3Dihub</t>
@@ -3157,7 +3156,7 @@
     <t xml:space="preserve">ylai5@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Marinemicroalgae", "Dunaliellaviridis", "Flocculation", "Harvesting", "Waterreuse", "Dissolvedorganicmatter")</t>
+    <t xml:space="preserve">Marinemicroalgae; Dunaliellaviridis; Flocculation; Harvesting; Waterreuse; Dissolvedorganicmatter</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0277379123002019</t>
@@ -3184,10 +3183,10 @@
     <t xml:space="preserve">Data are reposited at www.neotomadb.org and https://www.ncei.noaa.gov. Code for analogs and paleoclimate reconstructions are available at https://github.com/davidfastovich/gds_climate_reconstruction.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("https://www.ncei.noaa.gov", "https://github.com/davidfastovich/gds_climate_reconstruction")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("Palynology", "Plantmacrofossil", "Charcoal", "Paleoclimatereconstruction", "Sea-levelrise", "Wildfire", "Wetlanddevelopment", "Hydroperiod")</t>
+    <t xml:space="preserve">https://www.ncei.noaa.gov; https://github.com/davidfastovich/gds_climate_reconstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palynology; Plantmacrofossil; Charcoal; Paleoclimatereconstruction; Sea-levelrise; Wildfire; Wetlanddevelopment; Hydroperiod</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969723018855</t>
@@ -3208,7 +3207,7 @@
     <t xml:space="preserve">The data will be posted at https://catalog.data.gov/dataset and available upon request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Microbiome", "Outdoorair", "Greenspace", "AirborneBacteria", "16SrRNA", "Aerobiome")</t>
+    <t xml:space="preserve">Microbiome; Outdoorair; Greenspace; AirborneBacteria; 16SrRNA; Aerobiome</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S2214109X23000062?via%3Dihub</t>
@@ -3250,7 +3249,7 @@
     <t xml:space="preserve">a.sohns@northeastern.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Watersecurity", "Textanalysis", "Structuraltopicmodeling", "Planning", "Environmentaljustice")</t>
+    <t xml:space="preserve">Watersecurity; Textanalysis; Structuraltopicmodeling; Planning; Environmentaljustice</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S004313542300444X?via%3Dihub</t>
@@ -3262,7 +3261,7 @@
     <t xml:space="preserve">0000-0001-8935-7759</t>
   </si>
   <si>
-    <t xml:space="preserve">c("crAssphage", "Municipaluntreatedwastewater", "Temporalvariations", "Spatialvariations", "Entericpathogenscorrelations", "Bacteria", "Andviruses", "qPCR", "rt-qPCR")</t>
+    <t xml:space="preserve">crAssphage; Municipaluntreatedwastewater; Temporalvariations; Spatialvariations; Entericpathogenscorrelations; Bacteria; Andviruses; qPCR; rt-qPCR</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969723000414</t>
@@ -3289,7 +3288,7 @@
     <t xml:space="preserve">not shareable</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Groundwatercontamination", "Swinelagoons", "Privatewells", "Atmosphericstressors", "Environmentalpollution")</t>
+    <t xml:space="preserve">Groundwatercontamination; Swinelagoons; Privatewells; Atmosphericstressors; Environmentalpollution</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969723015565?via%3Dihub</t>
@@ -3310,7 +3309,7 @@
     <t xml:space="preserve">jjkurkif@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Microplastics", "Streamflow", "Urbandevelopment", "Sediment", "Watershed", "Samplingmethod")</t>
+    <t xml:space="preserve">Microplastics; Streamflow; Urbandevelopment; Sediment; Watershed; Samplingmethod</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S1470160X23003321</t>
@@ -3337,7 +3336,7 @@
     <t xml:space="preserve">0000-0002-2843-4965</t>
   </si>
   <si>
-    <t xml:space="preserve">c("UAV", "UAS", "Rugosity", "Geomorphometry", "Coastalhabitat", "Remotesensing")</t>
+    <t xml:space="preserve">UAV; UAS; Rugosity; Geomorphometry; Coastalhabitat; Remotesensing</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S2589537023001359</t>
@@ -3349,7 +3348,7 @@
     <t xml:space="preserve">Environmental cleaning to prevent hospital-acquired infections on non-intensive care units: a pragmatic, single-centre, cluster randomized controlled, crossover trial comparing soap-based, disinfection and probiotic cleaning</t>
   </si>
   <si>
-    <t xml:space="preserve">c("docx", "pdf")</t>
+    <t xml:space="preserve">docx; pdf</t>
   </si>
   <si>
     <t xml:space="preserve">https://ars.els-cdn.com/content/image/1-s2.0-S2589537023001359-mmc1.docx</t>
@@ -3367,7 +3366,7 @@
     <t xml:space="preserve">0000-0002-1225-9023</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Hospital-aquiredinfection", "Multidrug-resistantpathogen", "Environmentalcleaning", "Probiotic", "Randomized-controlledtrial", "Environmentalhygiene", "MRSAVRE", "Multidrug-resistantGram-negative")</t>
+    <t xml:space="preserve">Hospital-aquiredinfection; Multidrug-resistantpathogen; Environmentalcleaning; Probiotic; Randomized-controlledtrial; Environmentalhygiene; MRSAVRE; Multidrug-resistantGram-negative</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0377026523000155</t>
@@ -3391,7 +3390,7 @@
     <t xml:space="preserve">0000-0001-6309-1403</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Atmosphericforcing", "CapeHatteras", "PEACH", "Atmosphericcyclones", "Atmosphericwarmandcoolseasons")</t>
+    <t xml:space="preserve">Atmosphericforcing; CapeHatteras; PEACH; Atmosphericcyclones; Atmosphericwarmandcoolseasons</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969723017424</t>
@@ -3418,7 +3417,7 @@
     <t xml:space="preserve">mriza@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Contamination", "Distribution", "Environment", "Healthimpact", "NorthCarolina", "PFASsources")</t>
+    <t xml:space="preserve">Contamination; Distribution; Environment; Healthimpact; NorthCarolina; PFASsources</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0169555X23000867</t>
@@ -3439,7 +3438,7 @@
     <t xml:space="preserve">jdp@uky.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Landscapechange", "Climatechange", "Attribution", "NeuseRiver", "Sea-levelrise", "Marshloss")</t>
+    <t xml:space="preserve">Landscapechange; Climatechange; Attribution; NeuseRiver; Sea-levelrise; Marshloss</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969722075118</t>
@@ -3460,7 +3459,7 @@
     <t xml:space="preserve">https://github.com/UNCSRP/CASS-IT</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Clustering", "Metals", "Privatewells", "Socialvulnerability", "Geographicdata")</t>
+    <t xml:space="preserve">Clustering; Metals; Privatewells; Socialvulnerability; Geographicdata</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969723000414?via%3Dihub</t>
@@ -3490,7 +3489,7 @@
     <t xml:space="preserve">0000-0003-0639-7865</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Microbioreactor", "Volatileorganiccompound", "Biofiltration", "Modeling")</t>
+    <t xml:space="preserve">Microbioreactor; Volatileorganiccompound; Biofiltration; Modeling</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0043135423000878?via%3Dihub</t>
@@ -3508,7 +3507,7 @@
     <t xml:space="preserve">Department of Civil, Construction, and Environmental Engineering, North Carolina State University, Raleigh, NC 27695, United States</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Biofiltration", "Cometabolism", "Adsorption", "Emergingcontaminants")</t>
+    <t xml:space="preserve">Biofiltration; Cometabolism; Adsorption; Emergingcontaminants</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0378377423000446</t>
@@ -3517,7 +3516,7 @@
     <t xml:space="preserve">Department of Biological and Agricultural Engineering, North Carolina State University, Raleigh, NC 27695–7625, USA</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Subsurfacedrainage", "Subirrigation", "On-farmwaterstorage", "Drainagewaterreuse", "Supplementalirrigation", "Surfacewaterquality")</t>
+    <t xml:space="preserve">Subsurfacedrainage; Subirrigation; On-farmwaterstorage; Drainagewaterreuse; Supplementalirrigation; Surfacewaterquality</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S209592732200593X?via%3Dihub</t>
@@ -3559,7 +3558,7 @@
     <t xml:space="preserve">kostas@ce.gatech.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Wastewater-basedepidemiology", "Passivesampling", "Mooreswab")</t>
+    <t xml:space="preserve">Wastewater-basedepidemiology; Passivesampling; Mooreswab</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0304389422024864</t>
@@ -3592,7 +3591,7 @@
     <t xml:space="preserve">The data that has been used is confidential.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("SARS-CoV-2", "Wastewater-basedepidemiology", "Universitycampus", "Emergingcontaminants", "Disinfectants")</t>
+    <t xml:space="preserve">SARS-CoV-2; Wastewater-basedepidemiology; Universitycampus; Emergingcontaminants; Disinfectants</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0743016722002844</t>
@@ -3616,7 +3615,7 @@
     <t xml:space="preserve">0000-0001-9333-9641</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Geographicinformationsystems", "Ruralgeography", "statisticalanalysis")</t>
+    <t xml:space="preserve">Geographicinformationsystems; Ruralgeography; statisticalanalysis</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969722079372</t>
@@ -3634,7 +3633,7 @@
     <t xml:space="preserve">etgay@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Forestedwatersheds", "FUTURESmodel", "Landuselandcoverchange(LULCC)", "Hydrologicmodeling", "SoilandWaterAssessmentTool(SWAT)", "Globalclimatemodel")</t>
+    <t xml:space="preserve">Forestedwatersheds; FUTURESmodel; Landuselandcoverchange(LULCC); Hydrologicmodeling; SoilandWaterAssessmentTool(SWAT); Globalclimatemodel</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0169772222001723</t>
@@ -3664,7 +3663,7 @@
     <t xml:space="preserve">The data used are given in online supplementary material associated with the paper.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("VOC", "Contaminantflux", "Groundwater", "Stream")</t>
+    <t xml:space="preserve">VOC; Contaminantflux; Groundwater; Stream</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0378383922001880</t>
@@ -3688,7 +3687,7 @@
     <t xml:space="preserve">0000-0001-7724-5805</t>
   </si>
   <si>
-    <t xml:space="preserve">c("CoastalaltimetrySealevel", "Waves", "Videocamera", "Tidegauge", "Buoy", "Altimeter", "Significantwaveheight", "Re-trackingalgorithm")</t>
+    <t xml:space="preserve">CoastalaltimetrySealevel; Waves; Videocamera; Tidegauge; Buoy; Altimeter; Significantwaveheight; Re-trackingalgorithm</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969722070966</t>
@@ -3712,7 +3711,7 @@
     <t xml:space="preserve">jill.stewart@unc.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Wastewater-basedepidemiology", "Sewagesurveillance", "Coronavirus", "COVID", "ddPCR")</t>
+    <t xml:space="preserve">Wastewater-basedepidemiology; Sewagesurveillance; Coronavirus; COVID; ddPCR</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969722075118?via%3Dihub</t>
@@ -3748,7 +3747,7 @@
     <t xml:space="preserve">0000-0003-4519-8156</t>
   </si>
   <si>
-    <t xml:space="preserve">c("GHGEmissions", "Waterextractable", "Phosphorus", "Zinc", "Copper", "NorthCarolina")</t>
+    <t xml:space="preserve">GHGEmissions; Waterextractable; Phosphorus; Zinc; Copper; NorthCarolina</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S2590061722000539</t>
@@ -3769,7 +3768,7 @@
     <t xml:space="preserve">wcurtis1@citadel.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Risk", "Compoundhazard", "Flood", "Rural", "Emergencymanagement", "Planning", "CCWE")</t>
+    <t xml:space="preserve">Risk; Compoundhazard; Flood; Rural; Emergencymanagement; Planning; CCWE</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S004896972205848X</t>
@@ -3796,7 +3795,7 @@
     <t xml:space="preserve">Larry.Engel@unc.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("ExtraintestinalpathogenicE.coli(ExPEC)", "Foodborneurinarytractinfection(fUTI)", "Concentratedanimalfeedingoperation(CAFO)", "Syndromicsurveillance", "Besag-York-Mollié(BYM)model", "Ecologicalregressionanalysis")</t>
+    <t xml:space="preserve">ExtraintestinalpathogenicE.coli(ExPEC); Foodborneurinarytractinfection(fUTI); Concentratedanimalfeedingoperation(CAFO); Syndromicsurveillance; Besag-York-Mollié(BYM)model; Ecologicalregressionanalysis</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969722059411</t>
@@ -3817,7 +3816,7 @@
     <t xml:space="preserve">djwallis@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Sourceapportionment", "Receptormodels", "PFAS", "Perfluoroalkylsubstances")</t>
+    <t xml:space="preserve">Sourceapportionment; Receptormodels; PFAS; Perfluoroalkylsubstances</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969722054821</t>
@@ -3844,7 +3843,7 @@
     <t xml:space="preserve">Code can be found at the Github linked in the article: https://github.com/haleyplaas/CR-AS_2020/blob/v0.1/CR-AS%20data%20cleaning%2C%20stats%2C%20figures.R. Data can be made available upon request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Waterquality", "ToxicCyanobacteria", "Airquality", "PM2.5", "Microcystis", "Dolichospermum")</t>
+    <t xml:space="preserve">Waterquality; ToxicCyanobacteria; Airquality; PM2.5; Microcystis; Dolichospermum</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0376738822006019</t>
@@ -3874,7 +3873,7 @@
     <t xml:space="preserve">0000-0002-7018-391X</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Permeance", "Selectivity", "Rejection", "Advectivetransport", "Diffusivetransport")</t>
+    <t xml:space="preserve">Permeance; Selectivity; Rejection; Advectivetransport; Diffusivetransport</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0301479722009070</t>
@@ -3907,7 +3906,7 @@
     <t xml:space="preserve">0000-0003-3896-1483</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Nutrientmanagement", "Livestock", "Agriculture", "Machinelearning", "SatelliteradarSentinel-1")</t>
+    <t xml:space="preserve">Nutrientmanagement; Livestock; Agriculture; Machinelearning; SatelliteradarSentinel-1</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0272771422002311</t>
@@ -3937,7 +3936,7 @@
     <t xml:space="preserve">Data are available in supplemental tables. Code will be shared upon request.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Nitrogenremoval", "Denitrification", "Anammox", "nosZ", "hzo", "Sediments")</t>
+    <t xml:space="preserve">Nitrogenremoval; Denitrification; Anammox; nosZ; hzo; Sediments</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969722019167</t>
@@ -3958,7 +3957,7 @@
     <t xml:space="preserve">arborqui@usc.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("CAFOs", "Swine", "Hogproduction", "Animalfarming", "Environmentaljustice", "Gastrointestinalillness")</t>
+    <t xml:space="preserve">CAFOs; Swine; Hogproduction; Animalfarming; Environmentaljustice; Gastrointestinalillness</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969722018563?via%3Dihub</t>
@@ -3970,7 +3969,7 @@
     <t xml:space="preserve">Department of Marine, Earth, and Atmospheric Sciences, North Carolina State University, Raleigh, NC, United States</t>
   </si>
   <si>
-    <t xml:space="preserve">c("PFAS", "Massload", "Model", "Sourcetracking", "Environmentalmonitoring", "Drinkingwater")</t>
+    <t xml:space="preserve">PFAS; Massload; Model; Sourcetracking; Environmentalmonitoring; Drinkingwater</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969722022951?via%3Dihub</t>
@@ -3997,7 +3996,7 @@
     <t xml:space="preserve">aharris5@ncsu.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Animalhusbandry", "Fecalcontamination", "Sanitation", "Hygiene", "Animalfecesmanagement", "Entericpathogens")</t>
+    <t xml:space="preserve">Animalhusbandry; Fecalcontamination; Sanitation; Hygiene; Animalfecesmanagement; Entericpathogens</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0925857422001574</t>
@@ -4009,7 +4008,7 @@
     <t xml:space="preserve">Department of Biological and Agricultural Engineering, North Carolina State University, 3100 Faucette Dr., Raleigh, NC 27695, United States of America</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Naturalinfrastructure", "Wetlandrestoration", "Reforestation", "Watershedmodeling")</t>
+    <t xml:space="preserve">Naturalinfrastructure; Wetlandrestoration; Reforestation; Watershedmodeling</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S027843432200142X</t>
@@ -4030,7 +4029,7 @@
     <t xml:space="preserve">nfiori@umich.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Hydrogeology", "Climatechange", "Sea-levelrise", "Saltwaterintrusion", "Barrier-islandaquifers")</t>
+    <t xml:space="preserve">Hydrogeology; Climatechange; Sea-levelrise; Saltwaterintrusion; Barrier-islandaquifers</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0043135422007552</t>
@@ -4051,7 +4050,7 @@
     <t xml:space="preserve">0000-0003-1322-1948</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Advancedmeteringinfrastructure", "Waterserviceinterruption", "WaterUtilities", "Smartmeters")</t>
+    <t xml:space="preserve">Advancedmeteringinfrastructure; Waterserviceinterruption; WaterUtilities; Smartmeters</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0160412022001027</t>
@@ -4081,7 +4080,7 @@
     <t xml:space="preserve">argos@uic.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Arsenic", "Privatewells", "Watercontamination", "Birthoutcomes", "Epidemiology")</t>
+    <t xml:space="preserve">Arsenic; Privatewells; Watercontamination; Birthoutcomes; Epidemiology</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969722002431</t>
@@ -4102,7 +4101,7 @@
     <t xml:space="preserve">yuezhi6170@163.com</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Lanthanumcontainingmaterial", "Lanthanumcarbonate", "Phosphorusremoval", "Wastewatertreatment", "Mineralprecipitation")</t>
+    <t xml:space="preserve">Lanthanumcontainingmaterial; Lanthanumcarbonate; Phosphorusremoval; Wastewatertreatment; Mineralprecipitation</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969722024949?via%3Dihub</t>
@@ -4126,7 +4125,7 @@
     <t xml:space="preserve">sonia.grego@duke.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Residencehall", "Asymptomaticsurveillance", "Positivepredictivevalue", "Clinicalcase")</t>
+    <t xml:space="preserve">Residencehall; Asymptomaticsurveillance; Positivepredictivevalue; Clinicalcase</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0301479722005771</t>
@@ -4153,7 +4152,7 @@
     <t xml:space="preserve">0000-0001-6020-9250</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Infiltrationcapacity", "Urbanhydrology", "Urbansoil", "Rainfall-runoffmodels", "Randomforest", "Stormwater")</t>
+    <t xml:space="preserve">Infiltrationcapacity; Urbanhydrology; Urbansoil; Rainfall-runoffmodels; Randomforest; Stormwater</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S2352801X22000364</t>
@@ -4183,7 +4182,7 @@
     <t xml:space="preserve">0000-0002-4606-9973</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Groundwater", "Microbesampling", "NorthCarolina", "Coliform", "E.coli", "Waterquality")</t>
+    <t xml:space="preserve">Groundwater; Microbesampling; NorthCarolina; Coliform; E.coli; Waterquality</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S2772411522000088</t>
@@ -4198,7 +4197,7 @@
     <t xml:space="preserve">Department of Forestry and Environmental Resources, North Carolina State University, Raleigh, N.C., U.SA.</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Rurallandscapes", "Nature-basedsolutions", "Costs", "Economics", "Capitalbudgeting", "Floodmitigation")</t>
+    <t xml:space="preserve">Rurallandscapes; Nature-basedsolutions; Costs; Economics; Capitalbudgeting; Floodmitigation</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S014362282200008X</t>
@@ -4222,7 +4221,7 @@
     <t xml:space="preserve">0000-0002-9380-7625</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Aquaticecosystems", "Hydrology", "Landuse/landcover", "Physicalhabitat", "Urbanstreams", "Waterquality")</t>
+    <t xml:space="preserve">Aquaticecosystems; Hydrology; Landuse/landcover; Physicalhabitat; Urbanstreams; Waterquality</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S0048969721075811</t>
@@ -4246,7 +4245,7 @@
     <t xml:space="preserve">mmunir@uncc.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">c("SARS-CoV-2", "Wastewater", "COVID-19", "RT-qPCR", "RT-ddPCR", "Wastewater-basedepidemiology(WBE)")</t>
+    <t xml:space="preserve">SARS-CoV-2; Wastewater; COVID-19; RT-qPCR; RT-ddPCR; Wastewater-basedepidemiology(WBE)</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0378377422001391</t>
@@ -4261,7 +4260,7 @@
     <t xml:space="preserve">Department of Biological and Agricultural Engineering, North Carolina State University, Weaver Laboratory, 3110 Faucette Dr., Raleigh, NC 27695-7625, USA</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Subsurfacedrainage", "Supplementalirrigation", "On-farmwaterstorage", "Irrigationreservoir", "Drainagewaterreuse", "DRAINMOD-DWR")</t>
+    <t xml:space="preserve">Subsurfacedrainage; Supplementalirrigation; On-farmwaterstorage; Irrigationreservoir; Drainagewaterreuse; DRAINMOD-DWR</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969722019167?via%3Dihub</t>
@@ -4276,7 +4275,7 @@
     <t xml:space="preserve">https://ars.els-cdn.com/content/image/1-s2.0-S0048969721065578-mmc1.docx</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Arsenic", "Manganese", "Lead", "Privatewells", "K-meansclustering", "Geocoding")</t>
+    <t xml:space="preserve">Arsenic; Manganese; Lead; Privatewells; K-meansclustering; Geocoding</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/abs/pii/S0048969721061866</t>
@@ -4288,7 +4287,7 @@
     <t xml:space="preserve">https://ars.els-cdn.com/content/image/1-s2.0-S0048969721061866-mmc1.docx</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Floods", "Hurricanes", "Interruptedtimeseriesanalysis", "Gastrointestinalillness", "Environmentalepidemiology", "Disasterepidemiology")</t>
+    <t xml:space="preserve">Floods; Hurricanes; Interruptedtimeseriesanalysis; Gastrointestinalillness; Environmentalepidemiology; Disasterepidemiology</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S001393512101447X</t>
@@ -4309,7 +4308,7 @@
     <t xml:space="preserve">Department of Environmental Sciences and Engineering, Gillings School of Global Public Health, University of North Carolina at Chapel Hill, 135 Dauer Drive, Chapel Hill, NC, 27599, USA</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Bayesiannetworks", "Drinkingwater", "Bloodleadlevels", "Machinelearning", "Riskassessment", "Healthdisparity")</t>
+    <t xml:space="preserve">Bayesiannetworks; Drinkingwater; Bloodleadlevels; Machinelearning; Riskassessment; Healthdisparity</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.sciencedirect.com/science/article/pii/S004896972105525X</t>
@@ -4324,7 +4323,7 @@
     <t xml:space="preserve">University of North Carolina at Chapel Hill, Gillings School of Global Public Health, Department of Environmental Science &amp; Engineering, 135 Dauer Drive, Chapel Hill, NC 27599, United States of America</t>
   </si>
   <si>
-    <t xml:space="preserve">c("Privatewells", "Householdwatertreatment", "Healthbeliefmodel", "Self-efficacy", "Socialcognitivetheory", "Drinkingwater")</t>
+    <t xml:space="preserve">Privatewells; Householdwatertreatment; Healthbeliefmodel; Self-efficacy; Socialcognitivetheory; Drinkingwater</t>
   </si>
 </sst>
 </file>

--- a/inst/extdata/uncnewsletter.xlsx
+++ b/inst/extdata/uncnewsletter.xlsx
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">biology-geologyfeebacks; DMQ99; evapotranspiration; headwaterstreams; landusechange; seasonalflashiness; specificconductance; streamgauges</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scholar.google.com/scholar_url?url=https://ajph.aphapublications.org/doi/pdf/10.2105/AJPH.2022.307003%3Fdownload%3Dtrue&amp;hl=en&amp;sa=X&amp;d=3962241131938486649&amp;ei=H1Q7Y6aFPO2KywSS3bH4Bg&amp;scisig=AAGBfm3Q4X2sCbJJGTgTcSrsGU_FdUVJcw&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:7463423130094204642:AAGBfm306n8jEm7p9E06Y9mqflGSBiV6Pg&amp;html=&amp;pos=0&amp;folt=kw-top</t>
+    <t xml:space="preserve">https://ajph.aphapublications.org/doi/pdf/10.2105/AJPH.2022.307003?download=true</t>
   </si>
   <si>
     <t xml:space="preserve">scholar.google.com</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">0000-0003-3641-737X</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scholar.google.com/scholar_url?url=https://pubs.acs.org/doi/full/10.1021/acsestwater.2c00157&amp;hl=en&amp;sa=X&amp;d=1709742523088559831&amp;ei=Dg_7YtkJhJjLBKCbvNAC&amp;scisig=AAGBfm0jov0_aWmZMwe4s6j4e9vubbdcbA&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:3226461804228696973:AAGBfm3ju-C3kL6mSiPesevK78XQ69Qd6A&amp;html=&amp;pos=2&amp;folt=kw</t>
+    <t xml:space="preserve">https://pubs.acs.org/doi/full/10.1021/acsestwater.2c00157</t>
   </si>
   <si>
     <t xml:space="preserve">ACS EST Water</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">WASP; environmentalmodeling; nanocopper; nanomaterials; freswater</t>
   </si>
   <si>
-    <t xml:space="preserve">https://scholar.google.com/scholar_url?url=https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/hir.12445&amp;hl=en&amp;sa=X&amp;d=7293212103073901469&amp;ei=2fm2YrzQKtHjmQGNwb84&amp;scisig=AAGBfm1zjx3-V2aCgS0L1xZx26MYDvF-tg&amp;oi=scholaralrt&amp;hist=hZvSJggAAAAJ:3552202248086981277:AAGBfm3xoOKMdpREzJ__fgBb7pdlMpLHFA&amp;html=&amp;pos=1&amp;folt=kw</t>
+    <t xml:space="preserve">https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/hir.12445</t>
   </si>
   <si>
     <t xml:space="preserve">Health Information and Libraries Journal</t>
